--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/13.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/13.xlsx
@@ -426,13 +426,13 @@
         <v>-9.190494055966342</v>
       </c>
       <c r="E2">
-        <v>-14.33046675735663</v>
+        <v>-25.38203096258984</v>
       </c>
       <c r="F2">
-        <v>-0.4978009110206483</v>
+        <v>-2.419219810999171</v>
       </c>
       <c r="G2">
-        <v>-11.15418250958827</v>
+        <v>-14.86826865264169</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.170390848454947</v>
       </c>
       <c r="E3">
-        <v>-14.48842445921818</v>
+        <v>-25.37606243384773</v>
       </c>
       <c r="F3">
-        <v>-0.3079349604619876</v>
+        <v>-2.468858070877126</v>
       </c>
       <c r="G3">
-        <v>-11.79566691873285</v>
+        <v>-14.48777772217664</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.020933288654454</v>
       </c>
       <c r="E4">
-        <v>-14.90605391762757</v>
+        <v>-25.76412548546103</v>
       </c>
       <c r="F4">
-        <v>-0.5584473453144057</v>
+        <v>-2.492705111668919</v>
       </c>
       <c r="G4">
-        <v>-11.24981754912674</v>
+        <v>-14.50356736912619</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.737526292365041</v>
       </c>
       <c r="E5">
-        <v>-15.42723146269634</v>
+        <v>-26.67664922579867</v>
       </c>
       <c r="F5">
-        <v>-0.04718975308278719</v>
+        <v>-2.389745670440163</v>
       </c>
       <c r="G5">
-        <v>-11.92702605518559</v>
+        <v>-14.34996467719509</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.327042223850562</v>
       </c>
       <c r="E6">
-        <v>-16.19872946548711</v>
+        <v>-26.3575050201081</v>
       </c>
       <c r="F6">
-        <v>-0.3742963014676587</v>
+        <v>-2.591929444278452</v>
       </c>
       <c r="G6">
-        <v>-11.19306817749255</v>
+        <v>-14.28247093001319</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.808262573332107</v>
       </c>
       <c r="E7">
-        <v>-16.17613238018883</v>
+        <v>-27.54783252692029</v>
       </c>
       <c r="F7">
-        <v>0.07890681807356195</v>
+        <v>-2.563616674818167</v>
       </c>
       <c r="G7">
-        <v>-10.3819580360068</v>
+        <v>-14.27745048770289</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.202549592304575</v>
       </c>
       <c r="E8">
-        <v>-15.89767198498317</v>
+        <v>-27.0189701614605</v>
       </c>
       <c r="F8">
-        <v>-0.01492981294816324</v>
+        <v>-2.084188271671717</v>
       </c>
       <c r="G8">
-        <v>-10.86173553774013</v>
+        <v>-13.77464317592561</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.526761438317112</v>
       </c>
       <c r="E9">
-        <v>-17.03982558530176</v>
+        <v>-28.05406610776375</v>
       </c>
       <c r="F9">
-        <v>0.08309255855990785</v>
+        <v>-2.313554921832872</v>
       </c>
       <c r="G9">
-        <v>-10.38378876769001</v>
+        <v>-13.57315344276895</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.800449875963752</v>
       </c>
       <c r="E10">
-        <v>-17.86743138104756</v>
+        <v>-27.92305282624784</v>
       </c>
       <c r="F10">
-        <v>0.1491739113834328</v>
+        <v>-2.200349404198889</v>
       </c>
       <c r="G10">
-        <v>-9.027703240620514</v>
+        <v>-13.30633174866754</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.046245317068832</v>
       </c>
       <c r="E11">
-        <v>-18.48031505324567</v>
+        <v>-28.74171035735448</v>
       </c>
       <c r="F11">
-        <v>0.4125309611836601</v>
+        <v>-2.324137315403636</v>
       </c>
       <c r="G11">
-        <v>-9.55246443514147</v>
+        <v>-13.2482714009998</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.277720042807722</v>
       </c>
       <c r="E12">
-        <v>-19.40646044339838</v>
+        <v>-29.441622243032</v>
       </c>
       <c r="F12">
-        <v>0.3886988310051183</v>
+        <v>-2.230754629718645</v>
       </c>
       <c r="G12">
-        <v>-9.163472023731567</v>
+        <v>-12.91759093871862</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.502304718559189</v>
       </c>
       <c r="E13">
-        <v>-19.4029282336724</v>
+        <v>-29.49447859164953</v>
       </c>
       <c r="F13">
-        <v>0.1474036902436503</v>
+        <v>-2.204646974284613</v>
       </c>
       <c r="G13">
-        <v>-8.791757349491119</v>
+        <v>-12.57309556990206</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.737077664820701</v>
       </c>
       <c r="E14">
-        <v>-20.52972577863098</v>
+        <v>-30.28412671826304</v>
       </c>
       <c r="F14">
-        <v>0.4798830296030794</v>
+        <v>-2.203323243174939</v>
       </c>
       <c r="G14">
-        <v>-7.785414405917924</v>
+        <v>-12.29095763686321</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.98944946278449</v>
       </c>
       <c r="E15">
-        <v>-22.07792500084733</v>
+        <v>-31.1674395370142</v>
       </c>
       <c r="F15">
-        <v>0.8244780705958542</v>
+        <v>-1.756719726731822</v>
       </c>
       <c r="G15">
-        <v>-7.352957842122929</v>
+        <v>-11.69558581653514</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.264431679896464</v>
       </c>
       <c r="E16">
-        <v>-23.08186957445181</v>
+        <v>-31.39497044929259</v>
       </c>
       <c r="F16">
-        <v>1.086437664587559</v>
+        <v>-1.806985889101099</v>
       </c>
       <c r="G16">
-        <v>-6.851039411822946</v>
+        <v>-11.27095538239499</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.5714614292890153</v>
       </c>
       <c r="E17">
-        <v>-22.98708861347127</v>
+        <v>-32.42352048641776</v>
       </c>
       <c r="F17">
-        <v>1.271675526466779</v>
+        <v>-1.894727392773025</v>
       </c>
       <c r="G17">
-        <v>-5.579306585094076</v>
+        <v>-11.50583527786074</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.08478192437361408</v>
       </c>
       <c r="E18">
-        <v>-23.79096067694288</v>
+        <v>-33.02482937905226</v>
       </c>
       <c r="F18">
-        <v>1.152712027015936</v>
+        <v>-1.706130501075453</v>
       </c>
       <c r="G18">
-        <v>-5.729999307496161</v>
+        <v>-10.54842881844905</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.7003177803668332</v>
       </c>
       <c r="E19">
-        <v>-24.87030887124908</v>
+        <v>-33.80281668509602</v>
       </c>
       <c r="F19">
-        <v>1.186028963956532</v>
+        <v>-1.479610121310317</v>
       </c>
       <c r="G19">
-        <v>-5.65160227858068</v>
+        <v>-10.76961298701884</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.269688420081818</v>
       </c>
       <c r="E20">
-        <v>-25.95258245976424</v>
+        <v>-34.72299128226962</v>
       </c>
       <c r="F20">
-        <v>1.297532186577762</v>
+        <v>-1.474335906056693</v>
       </c>
       <c r="G20">
-        <v>-4.84414697937028</v>
+        <v>-10.6880841820232</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.785636372843309</v>
       </c>
       <c r="E21">
-        <v>-26.81815498159036</v>
+        <v>-34.84110520557468</v>
       </c>
       <c r="F21">
-        <v>1.429706489368451</v>
+        <v>-1.347014179511604</v>
       </c>
       <c r="G21">
-        <v>-5.063781812627688</v>
+        <v>-10.35124610503898</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.241529664344228</v>
       </c>
       <c r="E22">
-        <v>-27.67613778097961</v>
+        <v>-35.36581722460644</v>
       </c>
       <c r="F22">
-        <v>1.531418409288591</v>
+        <v>-1.027577484909252</v>
       </c>
       <c r="G22">
-        <v>-4.4304314138731</v>
+        <v>-10.26522157920102</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.631416324151297</v>
       </c>
       <c r="E23">
-        <v>-26.97784256052283</v>
+        <v>-36.47289779373562</v>
       </c>
       <c r="F23">
-        <v>2.090607824548398</v>
+        <v>-1.122924229706281</v>
       </c>
       <c r="G23">
-        <v>-4.289908687367656</v>
+        <v>-10.12707251384723</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.948926831718294</v>
       </c>
       <c r="E24">
-        <v>-28.4126397366391</v>
+        <v>-36.22446570967482</v>
       </c>
       <c r="F24">
-        <v>1.679696174389703</v>
+        <v>-0.7266440329832341</v>
       </c>
       <c r="G24">
-        <v>-4.008144845974745</v>
+        <v>-9.692467405997249</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.191518334724961</v>
       </c>
       <c r="E25">
-        <v>-28.19238381785403</v>
+        <v>-36.42909839313343</v>
       </c>
       <c r="F25">
-        <v>1.874407245887338</v>
+        <v>-0.7149276044380378</v>
       </c>
       <c r="G25">
-        <v>-2.969001017198452</v>
+        <v>-10.32455979744691</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.358687102301675</v>
       </c>
       <c r="E26">
-        <v>-29.10087268785084</v>
+        <v>-36.56951731516327</v>
       </c>
       <c r="F26">
-        <v>1.974015112604367</v>
+        <v>-0.7107435206864976</v>
       </c>
       <c r="G26">
-        <v>-3.779727135401652</v>
+        <v>-10.1425724880621</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.449875239629235</v>
       </c>
       <c r="E27">
-        <v>-29.01467771358884</v>
+        <v>-36.83223447048127</v>
       </c>
       <c r="F27">
-        <v>2.009233981101791</v>
+        <v>-0.8094915420394211</v>
       </c>
       <c r="G27">
-        <v>-3.582541111446042</v>
+        <v>-10.24532520051</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.466200357222752</v>
       </c>
       <c r="E28">
-        <v>-28.81637583679295</v>
+        <v>-36.76378205738132</v>
       </c>
       <c r="F28">
-        <v>2.107774910604015</v>
+        <v>-0.6568375119493197</v>
       </c>
       <c r="G28">
-        <v>-3.509179422295792</v>
+        <v>-10.54641931730671</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.40870190488823</v>
       </c>
       <c r="E29">
-        <v>-28.70610296623217</v>
+        <v>-36.59162985374273</v>
       </c>
       <c r="F29">
-        <v>2.148446093346665</v>
+        <v>-0.6856555855253117</v>
       </c>
       <c r="G29">
-        <v>-4.222893314016189</v>
+        <v>-10.19939800224369</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.277600575617012</v>
       </c>
       <c r="E30">
-        <v>-28.14528315970026</v>
+        <v>-36.2546208180919</v>
       </c>
       <c r="F30">
-        <v>1.919849824870113</v>
+        <v>-0.6494716690036265</v>
       </c>
       <c r="G30">
-        <v>-4.001063589066244</v>
+        <v>-10.0128355189236</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.072451682654616</v>
       </c>
       <c r="E31">
-        <v>-28.20137283875926</v>
+        <v>-36.4233517596177</v>
       </c>
       <c r="F31">
-        <v>2.133291940079851</v>
+        <v>-0.5691838152220901</v>
       </c>
       <c r="G31">
-        <v>-3.682148805631633</v>
+        <v>-10.30149853722035</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.794703194217926</v>
       </c>
       <c r="E32">
-        <v>-27.65769783482038</v>
+        <v>-36.19121086079949</v>
       </c>
       <c r="F32">
-        <v>2.041223873463102</v>
+        <v>-0.669520645253583</v>
       </c>
       <c r="G32">
-        <v>-3.873346052706701</v>
+        <v>-10.53135302455749</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.44529039993135</v>
       </c>
       <c r="E33">
-        <v>-28.00382268864865</v>
+        <v>-35.59659958122234</v>
       </c>
       <c r="F33">
-        <v>1.835261915900644</v>
+        <v>-0.6832905965903191</v>
       </c>
       <c r="G33">
-        <v>-3.769815362057074</v>
+        <v>-10.47507375038988</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.026549981371229</v>
       </c>
       <c r="E34">
-        <v>-27.84743183879375</v>
+        <v>-35.50352359070569</v>
       </c>
       <c r="F34">
-        <v>2.362184764086604</v>
+        <v>-0.4416839896853986</v>
       </c>
       <c r="G34">
-        <v>-4.524599881737669</v>
+        <v>-10.93813630769544</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.543661120800596</v>
       </c>
       <c r="E35">
-        <v>-28.01084182336054</v>
+        <v>-35.31208688050543</v>
       </c>
       <c r="F35">
-        <v>2.257144463942016</v>
+        <v>-0.7261345870305124</v>
       </c>
       <c r="G35">
-        <v>-5.312387229899258</v>
+        <v>-11.26177855016013</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.00266579458627</v>
       </c>
       <c r="E36">
-        <v>-27.37918762640064</v>
+        <v>-34.79190786395535</v>
       </c>
       <c r="F36">
-        <v>2.208116710839924</v>
+        <v>-0.7319000241539969</v>
       </c>
       <c r="G36">
-        <v>-4.989940094374244</v>
+        <v>-11.01762581663888</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.411487828428824</v>
       </c>
       <c r="E37">
-        <v>-25.84945099271356</v>
+        <v>-34.44695362065806</v>
       </c>
       <c r="F37">
-        <v>2.694954860404416</v>
+        <v>-0.4478785211235333</v>
       </c>
       <c r="G37">
-        <v>-5.183977789522007</v>
+        <v>-10.70068742889121</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.2207152096424945</v>
       </c>
       <c r="E38">
-        <v>-25.74961625474046</v>
+        <v>-33.72661152449494</v>
       </c>
       <c r="F38">
-        <v>2.352098562590118</v>
+        <v>-0.7786679909812514</v>
       </c>
       <c r="G38">
-        <v>-5.604622326832883</v>
+        <v>-11.13167742101231</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.8838628397216837</v>
       </c>
       <c r="E39">
-        <v>-25.06775486645752</v>
+        <v>-32.99491201552058</v>
       </c>
       <c r="F39">
-        <v>2.329361534118077</v>
+        <v>-0.4210104244137313</v>
       </c>
       <c r="G39">
-        <v>-5.335902034864701</v>
+        <v>-11.36638516811002</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.568936366718849</v>
       </c>
       <c r="E40">
-        <v>-24.67168094432465</v>
+        <v>-32.72242694176805</v>
       </c>
       <c r="F40">
-        <v>2.307257378341775</v>
+        <v>-0.4537657282552293</v>
       </c>
       <c r="G40">
-        <v>-5.302869411473853</v>
+        <v>-11.00418500174944</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.26719188221746</v>
       </c>
       <c r="E41">
-        <v>-24.81242591648304</v>
+        <v>-32.44760970390156</v>
       </c>
       <c r="F41">
-        <v>2.712191529321868</v>
+        <v>-0.2985909761584091</v>
       </c>
       <c r="G41">
-        <v>-5.881787820471745</v>
+        <v>-11.05869313405353</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.96520426409911</v>
       </c>
       <c r="E42">
-        <v>-23.51150401745553</v>
+        <v>-32.06711146811807</v>
       </c>
       <c r="F42">
-        <v>2.928186672867034</v>
+        <v>-0.2660941229465845</v>
       </c>
       <c r="G42">
-        <v>-5.522739293464549</v>
+        <v>-11.17109608674841</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.657449438422388</v>
       </c>
       <c r="E43">
-        <v>-22.39658918829308</v>
+        <v>-31.12588173104581</v>
       </c>
       <c r="F43">
-        <v>2.827937649780238</v>
+        <v>-0.2805690149431031</v>
       </c>
       <c r="G43">
-        <v>-5.793538608031393</v>
+        <v>-11.59699114928457</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.337476654369686</v>
       </c>
       <c r="E44">
-        <v>-21.44179214309384</v>
+        <v>-30.6280054489835</v>
       </c>
       <c r="F44">
-        <v>2.614306666802662</v>
+        <v>-0.1049335879971351</v>
       </c>
       <c r="G44">
-        <v>-6.961634806653378</v>
+        <v>-11.26548305061857</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.993073697419415</v>
       </c>
       <c r="E45">
-        <v>-21.92041108943853</v>
+        <v>-30.10375307006352</v>
       </c>
       <c r="F45">
-        <v>2.55951181984228</v>
+        <v>-0.1601045137583878</v>
       </c>
       <c r="G45">
-        <v>-5.961459409419845</v>
+        <v>-11.38458985803047</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.621565066900238</v>
       </c>
       <c r="E46">
-        <v>-21.3447695874795</v>
+        <v>-29.84448434770237</v>
       </c>
       <c r="F46">
-        <v>2.713487095939847</v>
+        <v>-0.0001252307253304775</v>
       </c>
       <c r="G46">
-        <v>-6.760856840787659</v>
+        <v>-11.41303406530389</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.220980519531421</v>
       </c>
       <c r="E47">
-        <v>-20.28246656933817</v>
+        <v>-29.17819638153181</v>
       </c>
       <c r="F47">
-        <v>2.717741590920625</v>
+        <v>-0.3407996088006551</v>
       </c>
       <c r="G47">
-        <v>-6.343105720278106</v>
+        <v>-11.7299592108694</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.784323444946948</v>
       </c>
       <c r="E48">
-        <v>-20.0276176376085</v>
+        <v>-28.50176463358406</v>
       </c>
       <c r="F48">
-        <v>2.755647683272731</v>
+        <v>-0.2085872011094373</v>
       </c>
       <c r="G48">
-        <v>-6.149670544418491</v>
+        <v>-11.56304812587042</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.307672971544271</v>
       </c>
       <c r="E49">
-        <v>-18.40951689060975</v>
+        <v>-27.9914554261337</v>
       </c>
       <c r="F49">
-        <v>2.822816682496131</v>
+        <v>-0.1493108864999102</v>
       </c>
       <c r="G49">
-        <v>-6.716041985822545</v>
+        <v>-11.44416974610073</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.792976034651384</v>
       </c>
       <c r="E50">
-        <v>-17.73899027276801</v>
+        <v>-28.15509183440087</v>
       </c>
       <c r="F50">
-        <v>2.94356614206741</v>
+        <v>-0.0381191300221326</v>
       </c>
       <c r="G50">
-        <v>-6.768838566082842</v>
+        <v>-11.53778535286024</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.236759366592578</v>
       </c>
       <c r="E51">
-        <v>-18.17371019208234</v>
+        <v>-27.0066300697896</v>
       </c>
       <c r="F51">
-        <v>2.842217047069695</v>
+        <v>-0.02272640694331219</v>
       </c>
       <c r="G51">
-        <v>-6.810382602055156</v>
+        <v>-11.6899512680273</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.630852490666095</v>
       </c>
       <c r="E52">
-        <v>-17.14253590426973</v>
+        <v>-27.1365746314397</v>
       </c>
       <c r="F52">
-        <v>2.729295659454873</v>
+        <v>-0.1535546127044521</v>
       </c>
       <c r="G52">
-        <v>-6.777869734313974</v>
+        <v>-11.98039204927864</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.979508153286975</v>
       </c>
       <c r="E53">
-        <v>-16.56854729532351</v>
+        <v>-26.28518981867962</v>
       </c>
       <c r="F53">
-        <v>2.670675411828363</v>
+        <v>0.03768145753843896</v>
       </c>
       <c r="G53">
-        <v>-6.777601580125292</v>
+        <v>-12.04993336887657</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.281151037520042</v>
       </c>
       <c r="E54">
-        <v>-16.79825866783659</v>
+        <v>-25.51986865443531</v>
       </c>
       <c r="F54">
-        <v>2.956695765401782</v>
+        <v>0.05376586739859696</v>
       </c>
       <c r="G54">
-        <v>-7.321954583147654</v>
+        <v>-11.85592215809313</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.524902800978516</v>
       </c>
       <c r="E55">
-        <v>-15.7259431936643</v>
+        <v>-25.08827791066028</v>
       </c>
       <c r="F55">
-        <v>2.806365305876533</v>
+        <v>-0.03830716942256809</v>
       </c>
       <c r="G55">
-        <v>-6.686793315983084</v>
+        <v>-12.13914595006885</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.717029983436772</v>
       </c>
       <c r="E56">
-        <v>-14.12299472069521</v>
+        <v>-25.17989346830946</v>
       </c>
       <c r="F56">
-        <v>2.662083585126526</v>
+        <v>0.1107393206283414</v>
       </c>
       <c r="G56">
-        <v>-6.76507778635023</v>
+        <v>-12.0027614054875</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.859534013694596</v>
       </c>
       <c r="E57">
-        <v>-14.68114725603662</v>
+        <v>-24.59725547400858</v>
       </c>
       <c r="F57">
-        <v>2.892987685187277</v>
+        <v>-0.09973972438158223</v>
       </c>
       <c r="G57">
-        <v>-7.566537687589009</v>
+        <v>-11.97712785137692</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.944371789068953</v>
       </c>
       <c r="E58">
-        <v>-13.82568228819562</v>
+        <v>-23.93949009592045</v>
       </c>
       <c r="F58">
-        <v>3.027027471369071</v>
+        <v>-0.01565794789522401</v>
       </c>
       <c r="G58">
-        <v>-7.41304755420624</v>
+        <v>-12.05761714507322</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.97445193771113</v>
       </c>
       <c r="E59">
-        <v>-13.3048262647814</v>
+        <v>-23.91626808120912</v>
       </c>
       <c r="F59">
-        <v>2.565837233330057</v>
+        <v>0.02089045028369298</v>
       </c>
       <c r="G59">
-        <v>-7.26618844353863</v>
+        <v>-12.22811024034569</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.954834182087875</v>
       </c>
       <c r="E60">
-        <v>-13.72660833385581</v>
+        <v>-23.38501468147328</v>
       </c>
       <c r="F60">
-        <v>2.549816607759915</v>
+        <v>-0.0647693661049983</v>
       </c>
       <c r="G60">
-        <v>-7.915594988158684</v>
+        <v>-12.35474853885943</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.880981373367646</v>
       </c>
       <c r="E61">
-        <v>-12.91043240650537</v>
+        <v>-23.76388040237701</v>
       </c>
       <c r="F61">
-        <v>2.257939696648704</v>
+        <v>0.01418895799504498</v>
       </c>
       <c r="G61">
-        <v>-7.236886804970542</v>
+        <v>-12.17024852541031</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.749433308000606</v>
       </c>
       <c r="E62">
-        <v>-11.28380001447617</v>
+        <v>-23.08691882297036</v>
       </c>
       <c r="F62">
-        <v>2.330234633360627</v>
+        <v>-0.1939217846102748</v>
       </c>
       <c r="G62">
-        <v>-7.137537333337013</v>
+        <v>-12.16522311728169</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.569395866194411</v>
       </c>
       <c r="E63">
-        <v>-12.22305986535509</v>
+        <v>-22.84525227907703</v>
       </c>
       <c r="F63">
-        <v>1.973761632179111</v>
+        <v>-0.2302539788970611</v>
       </c>
       <c r="G63">
-        <v>-7.439541850157028</v>
+        <v>-12.12871773162015</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.340230405445034</v>
       </c>
       <c r="E64">
-        <v>-12.3946301600837</v>
+        <v>-22.66299025721631</v>
       </c>
       <c r="F64">
-        <v>2.107135410969053</v>
+        <v>-0.2064732074974929</v>
       </c>
       <c r="G64">
-        <v>-6.71561161490244</v>
+        <v>-12.21061731771618</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.056194287159943</v>
       </c>
       <c r="E65">
-        <v>-10.56027666532266</v>
+        <v>-22.94320770033695</v>
       </c>
       <c r="F65">
-        <v>2.11860332929341</v>
+        <v>-0.2111650804669493</v>
       </c>
       <c r="G65">
-        <v>-6.874292683690786</v>
+        <v>-12.36295869179682</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.727502727908897</v>
       </c>
       <c r="E66">
-        <v>-12.52439358277349</v>
+        <v>-22.49957121570151</v>
       </c>
       <c r="F66">
-        <v>1.737521189309525</v>
+        <v>-0.4893838698408025</v>
       </c>
       <c r="G66">
-        <v>-6.345072184328433</v>
+        <v>-12.55850599571049</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.354416835117862</v>
       </c>
       <c r="E67">
-        <v>-11.66953995892354</v>
+        <v>-22.64525675300228</v>
       </c>
       <c r="F67">
-        <v>1.756083246071457</v>
+        <v>-0.5861935114711752</v>
       </c>
       <c r="G67">
-        <v>-6.927744751967859</v>
+        <v>-12.59049910780201</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.93047381024725</v>
       </c>
       <c r="E68">
-        <v>-11.24312073246527</v>
+        <v>-22.68704551114506</v>
       </c>
       <c r="F68">
-        <v>1.602803798592242</v>
+        <v>-0.7794847612404118</v>
       </c>
       <c r="G68">
-        <v>-7.048036734682817</v>
+        <v>-12.0311195385769</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.460589832186646</v>
       </c>
       <c r="E69">
-        <v>-10.44763087438186</v>
+        <v>-22.44901533187988</v>
       </c>
       <c r="F69">
-        <v>1.618981813968916</v>
+        <v>-0.6823106379528073</v>
       </c>
       <c r="G69">
-        <v>-7.084535499253281</v>
+        <v>-12.38497050908744</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.945729658500001</v>
       </c>
       <c r="E70">
-        <v>-11.33393022174108</v>
+        <v>-22.56461368787368</v>
       </c>
       <c r="F70">
-        <v>1.481443003877697</v>
+        <v>-0.8587653202601441</v>
       </c>
       <c r="G70">
-        <v>-6.379892502310488</v>
+        <v>-11.77676370370361</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.382046586807196</v>
       </c>
       <c r="E71">
-        <v>-10.7262588231258</v>
+        <v>-22.50624618638882</v>
       </c>
       <c r="F71">
-        <v>1.451459417365966</v>
+        <v>-0.980483141325295</v>
       </c>
       <c r="G71">
-        <v>-6.50425314549321</v>
+        <v>-11.77569439749443</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.770810924758416</v>
       </c>
       <c r="E72">
-        <v>-10.34155589922619</v>
+        <v>-22.46470196584245</v>
       </c>
       <c r="F72">
-        <v>1.179002751645987</v>
+        <v>-0.9489488510355234</v>
       </c>
       <c r="G72">
-        <v>-6.270614704604685</v>
+        <v>-11.88566740976348</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.116861239833418</v>
       </c>
       <c r="E73">
-        <v>-10.52403075936527</v>
+        <v>-21.88313269140739</v>
       </c>
       <c r="F73">
-        <v>1.011284860335976</v>
+        <v>-1.147291485227032</v>
       </c>
       <c r="G73">
-        <v>-6.351663480497122</v>
+        <v>-12.04974797832637</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.420044187627447</v>
       </c>
       <c r="E74">
-        <v>-10.52795694632992</v>
+        <v>-22.22150932620853</v>
       </c>
       <c r="F74">
-        <v>0.7140442702916381</v>
+        <v>-1.076774224961515</v>
       </c>
       <c r="G74">
-        <v>-5.438072091297689</v>
+        <v>-11.49962138388353</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.679049322549495</v>
       </c>
       <c r="E75">
-        <v>-11.39302227906717</v>
+        <v>-22.88215934223954</v>
       </c>
       <c r="F75">
-        <v>0.6653238414959852</v>
+        <v>-1.203991577213852</v>
       </c>
       <c r="G75">
-        <v>-5.949326260018417</v>
+        <v>-11.42483284960585</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.900806489975501</v>
       </c>
       <c r="E76">
-        <v>-11.79541342244074</v>
+        <v>-22.41539594084693</v>
       </c>
       <c r="F76">
-        <v>0.6584599891963885</v>
+        <v>-1.448076659387949</v>
       </c>
       <c r="G76">
-        <v>-5.579038430905395</v>
+        <v>-11.14251614710788</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.087010275880816</v>
       </c>
       <c r="E77">
-        <v>-11.62428238969088</v>
+        <v>-22.70610132976934</v>
       </c>
       <c r="F77">
-        <v>0.7948639359457719</v>
+        <v>-1.568141059117112</v>
       </c>
       <c r="G77">
-        <v>-5.172261768858527</v>
+        <v>-11.19132020944782</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.240998549586566</v>
       </c>
       <c r="E78">
-        <v>-11.66728477886772</v>
+        <v>-23.07168503640856</v>
       </c>
       <c r="F78">
-        <v>0.3440655669748781</v>
+        <v>-1.396934912673913</v>
       </c>
       <c r="G78">
-        <v>-5.471250378692265</v>
+        <v>-10.93213428863274</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.3728148207354644</v>
       </c>
       <c r="E79">
-        <v>-12.230676758636</v>
+        <v>-23.55980019274734</v>
       </c>
       <c r="F79">
-        <v>0.3628380290571205</v>
+        <v>-1.734859939339346</v>
       </c>
       <c r="G79">
-        <v>-4.836095732618773</v>
+        <v>-11.27369982464704</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.5087372611049521</v>
       </c>
       <c r="E80">
-        <v>-12.7418373191998</v>
+        <v>-23.44835444741857</v>
       </c>
       <c r="F80">
-        <v>0.6637159803671513</v>
+        <v>-1.683637012619836</v>
       </c>
       <c r="G80">
-        <v>-4.250728380910381</v>
+        <v>-10.8030428758744</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.388900308922456</v>
       </c>
       <c r="E81">
-        <v>-13.7154411169529</v>
+        <v>-24.30169103247595</v>
       </c>
       <c r="F81">
-        <v>0.4547462207651284</v>
+        <v>-1.734143401535924</v>
       </c>
       <c r="G81">
-        <v>-4.471747022203204</v>
+        <v>-10.46313261262973</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.254085152149864</v>
       </c>
       <c r="E82">
-        <v>-13.47826681927517</v>
+        <v>-24.24178384982848</v>
       </c>
       <c r="F82">
-        <v>0.3151166113492438</v>
+        <v>-1.844478626119207</v>
       </c>
       <c r="G82">
-        <v>-4.5818756301126</v>
+        <v>-10.84161735249798</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.088088208978123</v>
       </c>
       <c r="E83">
-        <v>-14.54945470341955</v>
+        <v>-25.01269767947226</v>
       </c>
       <c r="F83">
-        <v>0.08228904217919233</v>
+        <v>-1.847498853669814</v>
       </c>
       <c r="G83">
-        <v>-4.025756948243668</v>
+        <v>-10.96121412064969</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.872392548771269</v>
       </c>
       <c r="E84">
-        <v>-15.45776243445605</v>
+        <v>-25.7336397984414</v>
       </c>
       <c r="F84">
-        <v>0.3425256319730738</v>
+        <v>-1.843820902401385</v>
       </c>
       <c r="G84">
-        <v>-3.449811409140042</v>
+        <v>-10.61464966087109</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.591515918126283</v>
       </c>
       <c r="E85">
-        <v>-16.58028057147738</v>
+        <v>-26.37035230086786</v>
       </c>
       <c r="F85">
-        <v>0.2896542541219926</v>
+        <v>-1.940097075424354</v>
       </c>
       <c r="G85">
-        <v>-3.938401583098919</v>
+        <v>-10.67731166683842</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.229899002663634</v>
       </c>
       <c r="E86">
-        <v>-18.41507332821717</v>
+        <v>-27.17941852402627</v>
       </c>
       <c r="F86">
-        <v>0.05726323457321647</v>
+        <v>-2.097576345635763</v>
       </c>
       <c r="G86">
-        <v>-4.159145449111983</v>
+        <v>-10.70068742889121</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.772770224927449</v>
       </c>
       <c r="E87">
-        <v>-18.79877545936108</v>
+        <v>-28.23685796108336</v>
       </c>
       <c r="F87">
-        <v>0.05350493166671511</v>
+        <v>-2.116576608753775</v>
       </c>
       <c r="G87">
-        <v>-3.47007856893146</v>
+        <v>-10.48808088381367</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>6.208530053628672</v>
       </c>
       <c r="E88">
-        <v>-20.59116811396705</v>
+        <v>-28.62796867570383</v>
       </c>
       <c r="F88">
-        <v>0.3239900829680321</v>
+        <v>-2.12149876786121</v>
       </c>
       <c r="G88">
-        <v>-3.620979855702519</v>
+        <v>-10.42816332009841</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>6.529463990939995</v>
       </c>
       <c r="E89">
-        <v>-20.78733255103131</v>
+        <v>-30.00044499252654</v>
       </c>
       <c r="F89">
-        <v>-0.02959108761031169</v>
+        <v>-2.163203753122553</v>
       </c>
       <c r="G89">
-        <v>-3.213415283817304</v>
+        <v>-10.63563851959007</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>6.730417866365137</v>
       </c>
       <c r="E90">
-        <v>-22.87292125526389</v>
+        <v>-31.10304463662513</v>
       </c>
       <c r="F90">
-        <v>0.2646905740712267</v>
+        <v>-2.239142678039392</v>
       </c>
       <c r="G90">
-        <v>-3.614395180624909</v>
+        <v>-10.59370052869858</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>6.807242259172891</v>
       </c>
       <c r="E91">
-        <v>-24.89016622977272</v>
+        <v>-32.34592055582232</v>
       </c>
       <c r="F91">
-        <v>0.3598418241611947</v>
+        <v>-2.121935317482485</v>
       </c>
       <c r="G91">
-        <v>-3.849675652100912</v>
+        <v>-10.37790592826673</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>6.763821279812452</v>
       </c>
       <c r="E92">
-        <v>-26.2924444340399</v>
+        <v>-34.1307076383324</v>
       </c>
       <c r="F92">
-        <v>-0.1671448083147808</v>
+        <v>-2.499607897236447</v>
       </c>
       <c r="G92">
-        <v>-3.72226930702206</v>
+        <v>-10.90016103981446</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.606434466438507</v>
       </c>
       <c r="E93">
-        <v>-27.17142576740273</v>
+        <v>-34.66462830925876</v>
       </c>
       <c r="F93">
-        <v>0.4428111032255932</v>
+        <v>-2.568596819643798</v>
       </c>
       <c r="G93">
-        <v>-4.004053011688207</v>
+        <v>-10.95305031534985</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>6.340975955082829</v>
       </c>
       <c r="E94">
-        <v>-29.75739499982386</v>
+        <v>-35.93278217036677</v>
       </c>
       <c r="F94">
-        <v>0.3632629815347567</v>
+        <v>-2.693144343756912</v>
       </c>
       <c r="G94">
-        <v>-4.808830079557335</v>
+        <v>-10.92648649794274</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>5.984903680549227</v>
       </c>
       <c r="E95">
-        <v>-31.57942878104703</v>
+        <v>-37.53202861583458</v>
       </c>
       <c r="F95">
-        <v>0.2419154406986571</v>
+        <v>-2.568405466773751</v>
       </c>
       <c r="G95">
-        <v>-4.743996355716249</v>
+        <v>-10.99546502479899</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>5.550067746107001</v>
       </c>
       <c r="E96">
-        <v>-33.46694203218411</v>
+        <v>-39.50964265006527</v>
       </c>
       <c r="F96">
-        <v>0.2808785298567346</v>
+        <v>-2.893269624599244</v>
       </c>
       <c r="G96">
-        <v>-4.774503032860633</v>
+        <v>-10.97466817772129</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>5.05847195035832</v>
       </c>
       <c r="E97">
-        <v>-35.34374544229306</v>
+        <v>-40.78342993283883</v>
       </c>
       <c r="F97">
-        <v>0.08153108600563079</v>
+        <v>-3.118370182635982</v>
       </c>
       <c r="G97">
-        <v>-4.799673110595712</v>
+        <v>-11.68831916907644</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.509952130115443</v>
       </c>
       <c r="E98">
-        <v>-37.71284831872386</v>
+        <v>-42.17803916637402</v>
       </c>
       <c r="F98">
-        <v>-0.0929222606565423</v>
+        <v>-3.00669465959497</v>
       </c>
       <c r="G98">
-        <v>-5.278003903928387</v>
+        <v>-11.54037419947195</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.945063415046989</v>
       </c>
       <c r="E99">
-        <v>-40.2381314709682</v>
+        <v>-44.11221154944914</v>
       </c>
       <c r="F99">
-        <v>0.07658490424351494</v>
+        <v>-3.337245559640682</v>
       </c>
       <c r="G99">
-        <v>-5.098727931340234</v>
+        <v>-11.94774344917035</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.334435725829072</v>
       </c>
       <c r="E100">
-        <v>-42.55903100582435</v>
+        <v>-45.92742544881676</v>
       </c>
       <c r="F100">
-        <v>0.1633621882585828</v>
+        <v>-3.428629394782718</v>
       </c>
       <c r="G100">
-        <v>-5.016844897971901</v>
+        <v>-12.32893621528973</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.739200935309483</v>
       </c>
       <c r="E101">
-        <v>-44.91537717097555</v>
+        <v>-48.08822531360573</v>
       </c>
       <c r="F101">
-        <v>0.08363016900432474</v>
+        <v>-3.612647071477614</v>
       </c>
       <c r="G101">
-        <v>-5.736352244386023</v>
+        <v>-12.65345244177679</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.067670552673326</v>
       </c>
       <c r="E102">
-        <v>-46.62313717485216</v>
+        <v>-50.10529594186526</v>
       </c>
       <c r="F102">
-        <v>0.1299168543705527</v>
+        <v>-3.669869034928198</v>
       </c>
       <c r="G102">
-        <v>-5.896877287039743</v>
+        <v>-12.34004971666507</v>
       </c>
     </row>
   </sheetData>
